--- a/output/pdf_financials_xlsx/TRBE.xlsx
+++ b/output/pdf_financials_xlsx/TRBE.xlsx
@@ -3608,19 +3608,19 @@
         <v>0.142462</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.749832</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.453299</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.559808</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.872424</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.200776</v>
       </c>
     </row>
     <row r="93">
@@ -6468,7 +6468,11 @@
           <t>Reserve (Notes 13 and 14)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -7732,7 +7736,11 @@
           <t>Reserve (Notes 14 and 15)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TRBE.xlsx
+++ b/output/pdf_financials_xlsx/TRBE.xlsx
@@ -1757,10 +1757,10 @@
         <v>1.324101</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.81952</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.244547</v>
       </c>
     </row>
     <row r="35">
@@ -1819,10 +1819,10 @@
         <v>1.324101</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.81952</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.244547</v>
       </c>
     </row>
     <row r="37">
@@ -2191,10 +2191,10 @@
         <v>0.197241</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.0532</v>
+        <v>0.23368</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.80639</v>
+        <v>0.561843</v>
       </c>
     </row>
     <row r="49">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
